--- a/GroveCreaterKit.xlsx
+++ b/GroveCreaterKit.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/watanabekoichi/Developments/Claude_Projects/I0630_M5StackMicroPythonToolkit/I0630_M5StackMicroPythonTookkit/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/watanabekoichi/Developments/Claude_Projects/I0630_M5StackMicroPythonToolkit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BADEC3C-40B8-6447-AB6E-15B241FAD77C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8014201D-94EA-1F44-AD23-082E956F87ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2400" yWindow="660" windowWidth="31720" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9820" yWindow="840" windowWidth="31720" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Product Name</t>
   </si>
   <si>
     <t>概要</t>
@@ -911,6 +908,10 @@
   </si>
   <si>
     <t>○</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Product Name</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1369,921 +1370,921 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>5</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>10</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>11</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>18</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="12" t="s">
         <v>19</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H4" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J4" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="36" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="36" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>35</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="36" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>38</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>39</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="36" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>43</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="36" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>50</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="12" t="s">
         <v>51</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="36" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H10" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="36" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>62</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I11" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J11" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="36" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>66</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="36" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I13" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="36" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="E14" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>75</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H14" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I14" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>81</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J15" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="12" t="s">
         <v>82</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="36" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="F16" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J16" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K16" s="12" t="s">
         <v>88</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="36" customHeight="1">
       <c r="A17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>93</v>
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="36" customHeight="1">
       <c r="A18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="E18" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I18" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I18" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J18" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="36" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="E19" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K19" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="36" customHeight="1">
       <c r="A20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>106</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J20" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K20" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="36" customHeight="1">
       <c r="A21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I21" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J21" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="36" customHeight="1">
       <c r="A22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>114</v>
-      </c>
       <c r="F22" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J22" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="K22" s="12" t="s">
         <v>115</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J23" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="K23" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="36" customHeight="1">
       <c r="A24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="D24" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1">
       <c r="A25" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>131</v>
-      </c>
       <c r="E25" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="36" customHeight="1">
       <c r="A26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="D26" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="E26" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="F26" s="11"/>
       <c r="G26" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="36" customHeight="1">
       <c r="A27" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="6" t="s">
+      <c r="D27" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="E27" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>139</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H27" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I27" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I27" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J27" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="36" customHeight="1">
       <c r="A28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="6" t="s">
+      <c r="D28" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>144</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="36" customHeight="1">
       <c r="A29" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>148</v>
       </c>
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I29" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J29" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="14.25" customHeight="1">
@@ -2291,379 +2292,379 @@
         <v>104020111</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C30" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>152</v>
       </c>
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J30" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="K30" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="K30" s="12" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="36" customHeight="1">
       <c r="A31" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>159</v>
       </c>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H31" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I31" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I31" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J31" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="K31" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1">
       <c r="A32" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="6" t="s">
+      <c r="D32" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="E32" s="11" t="s">
         <v>164</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>165</v>
       </c>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I32" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I32" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J32" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="K32" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="36" customHeight="1">
       <c r="A33" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" s="6" t="s">
+      <c r="D33" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="E33" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="36" customHeight="1">
       <c r="A34" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="D34" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="E34" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>173</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I34" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="I34" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="J34" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K34" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="K34" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="36" customHeight="1">
       <c r="A35" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="6" t="s">
+      <c r="D35" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="E35" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
       <c r="H35" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="36" customHeight="1">
       <c r="A36" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="6" t="s">
+      <c r="D36" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="E36" s="11" t="s">
         <v>181</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>182</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="36" customHeight="1">
       <c r="A37" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="D37" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="E37" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E37" s="11" t="s">
-        <v>187</v>
-      </c>
       <c r="F37" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J37" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="K37" s="12" t="s">
         <v>188</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="18" customHeight="1">
       <c r="A38" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C38" s="6" t="s">
+      <c r="D38" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="E38" s="11" t="s">
         <v>192</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>193</v>
       </c>
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="36" customHeight="1">
       <c r="A39" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="6" t="s">
+      <c r="D39" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="E39" s="11" t="s">
         <v>197</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>198</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
       <c r="H39" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="36" customHeight="1">
       <c r="A40" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="6" t="s">
+      <c r="D40" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="E40" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="E40" s="11" t="s">
-        <v>203</v>
-      </c>
       <c r="F40" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J40" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="K40" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="K40" s="12" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="36" customHeight="1">
       <c r="A41" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="6" t="s">
+      <c r="D41" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="E41" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="E41" s="11" t="s">
-        <v>209</v>
-      </c>
       <c r="F41" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J41" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="K41" s="12" t="s">
         <v>210</v>
-      </c>
-      <c r="K41" s="12" t="s">
-        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/GroveCreaterKit.xlsx
+++ b/GroveCreaterKit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/watanabekoichi/Developments/Claude_Projects/I0630_M5StackMicroPythonToolkit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8014201D-94EA-1F44-AD23-082E956F87ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD5B9CC-E0D2-234F-9418-235DFA7B1DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9820" yWindow="840" windowWidth="31720" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="30240" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,9 +40,6 @@
     <t>設定コード</t>
   </si>
   <si>
-    <t>101020025</t>
-  </si>
-  <si>
     <t>Manual</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
 while True:
     print(p.value())
     time.sleep(0.2)</t>
-  </si>
-  <si>
-    <t>101020015</t>
   </si>
   <si>
     <t>input</t>
@@ -95,9 +89,6 @@
     print('%.1f C' % t); time.sleep(1)</t>
   </si>
   <si>
-    <t>101020018</t>
-  </si>
-  <si>
     <t>sensor</t>
   </si>
   <si>
@@ -116,9 +107,6 @@
 while True:
     print('WET' if w.value()==0 else 'dry')
     time.sleep(0.5)</t>
-  </si>
-  <si>
-    <t>101020017</t>
   </si>
   <si>
     <t>Grove - Rotary Angle Sensor</t>
@@ -139,9 +127,6 @@
     time.sleep(0.2)</t>
   </si>
   <si>
-    <t>101020023</t>
-  </si>
-  <si>
     <t>Grove - Sound Sensor</t>
   </si>
   <si>
@@ -151,9 +136,6 @@
     <t>騒音レベル監視、拍手スイッチ、音反応イルミネーション。</t>
   </si>
   <si>
-    <t>101020132</t>
-  </si>
-  <si>
     <t>Grove - Light Sensor v1.2</t>
   </si>
   <si>
@@ -161,9 +143,6 @@
   </si>
   <si>
     <t>自動照明制御、明暗判定、屋外/屋内の照度ロギング。</t>
-  </si>
-  <si>
-    <t>104030007</t>
   </si>
   <si>
     <t>Grove - Green LED</t>
@@ -186,9 +165,6 @@
     out.value(0); time.sleep(0.5)</t>
   </si>
   <si>
-    <t>107020000</t>
-  </si>
-  <si>
     <t>LED</t>
   </si>
   <si>
@@ -212,9 +188,6 @@
 buz.duty_u16(0)                       # 停止</t>
   </si>
   <si>
-    <t>101020038</t>
-  </si>
-  <si>
     <t>actuator</t>
   </si>
   <si>
@@ -227,9 +200,6 @@
     <t>ドア・窓の開閉検知、防犯センサー、位置検出。</t>
   </si>
   <si>
-    <t>101020172</t>
-  </si>
-  <si>
     <t>Input</t>
   </si>
   <si>
@@ -240,9 +210,6 @@
   </si>
   <si>
     <t>ライントレースロボット、エッジ検出、白黒コントラスト判定。</t>
-  </si>
-  <si>
-    <t>103020005</t>
   </si>
   <si>
     <t>Grove - Relay</t>
@@ -261,9 +228,6 @@
 relay.value(0)                  # OFF</t>
   </si>
   <si>
-    <t>101020586</t>
-  </si>
-  <si>
     <t>Grove - Vibration Sensor (SW-420)</t>
   </si>
   <si>
@@ -271,9 +235,6 @@
   </si>
   <si>
     <t>振動アラーム、機器の異常振動監視、盗難・接触検知。</t>
-  </si>
-  <si>
-    <t>101020011</t>
   </si>
   <si>
     <t>Grove - Temperature &amp; Humidity Sensor (DHT11)</t>
@@ -297,9 +258,6 @@
     time.sleep(2)</t>
   </si>
   <si>
-    <t>101020028</t>
-  </si>
-  <si>
     <t>Grove - Thumb Joystick</t>
   </si>
   <si>
@@ -321,9 +279,6 @@
     time.sleep(0.2)</t>
   </si>
   <si>
-    <t>104020048</t>
-  </si>
-  <si>
     <t>Grove - Chainable RGB Led V2.0</t>
   </si>
   <si>
@@ -344,9 +299,6 @@
 # led = P9813(clk, dat, 1); led[0]=(0,30,0); led.write()</t>
   </si>
   <si>
-    <t>104030014</t>
-  </si>
-  <si>
     <t>Grove - Multi Color Flash LED (5mm)</t>
   </si>
   <si>
@@ -361,9 +313,6 @@
 led.value(1)   # 通電すると自動で多色点滅</t>
   </si>
   <si>
-    <t>101020004</t>
-  </si>
-  <si>
     <t>Grove - Switch(P)</t>
   </si>
   <si>
@@ -373,9 +322,6 @@
     <t>電源・モードの手動切替、設定保持スイッチ、オンオフ入力。</t>
   </si>
   <si>
-    <t>104030005</t>
-  </si>
-  <si>
     <t>Grove - Red LED</t>
   </si>
   <si>
@@ -385,9 +331,6 @@
     <t>エラー/警告表示、状態インジケータ、通知ランプ。</t>
   </si>
   <si>
-    <t>104030010</t>
-  </si>
-  <si>
     <t>Grove - Blue LED</t>
   </si>
   <si>
@@ -397,9 +340,6 @@
     <t>状態表示、通知インジケータ、装飾ライト。</t>
   </si>
   <si>
-    <t>101020003</t>
-  </si>
-  <si>
     <t>Grove - Button</t>
   </si>
   <si>
@@ -407,9 +347,6 @@
   </si>
   <si>
     <t>ユーザー入力、トリガー操作、リセット/開始ボタン。</t>
-  </si>
-  <si>
-    <t>101020026</t>
   </si>
   <si>
     <t>Grove - Infrared Emitter</t>
@@ -427,9 +364,6 @@
     <t>from machine import Pin, PWM
 ir = PWM(Pin(9), freq=38000, duty_u16=32768)
 # 38kHzキャリア出力。送信にはNECなどの変調制御が必要</t>
-  </si>
-  <si>
-    <t>111020044</t>
   </si>
   <si>
     <t>wireless</t>
@@ -456,9 +390,6 @@
     time.sleep(0.05)</t>
   </si>
   <si>
-    <t>111020045</t>
-  </si>
-  <si>
     <t>Grove - Yellow LED Button</t>
   </si>
   <si>
@@ -475,18 +406,12 @@
     led.value(btn.value()); time.sleep(0.05)</t>
   </si>
   <si>
-    <t>111020046</t>
-  </si>
-  <si>
     <t>Grove - Blue LED Button</t>
   </si>
   <si>
     <t>青色LED内蔵のプッシュボタン。押下検知とLED点灯を同時に行える。</t>
   </si>
   <si>
-    <t>101020008</t>
-  </si>
-  <si>
     <t>Grove - Moisture Sensor</t>
   </si>
   <si>
@@ -494,9 +419,6 @@
   </si>
   <si>
     <t>植物の水やり管理、土壌湿度モニタ、自動潅水システム。</t>
-  </si>
-  <si>
-    <t>101020353</t>
   </si>
   <si>
     <t>Grove - Mini PIR Motion Sensor</t>
@@ -516,9 +438,6 @@
     time.sleep(0.2)</t>
   </si>
   <si>
-    <t>101020063</t>
-  </si>
-  <si>
     <t>Grove - Loudness Sensor</t>
   </si>
   <si>
@@ -526,9 +445,6 @@
   </si>
   <si>
     <t>騒音レベル監視、環境音モニタ、音反応デバイス。</t>
-  </si>
-  <si>
-    <t>101020016</t>
   </si>
   <si>
     <t>Grove - Infrared Receiver</t>
@@ -564,9 +480,6 @@
 i2c = I2C(0, scl=Pin(1), sda=Pin(2), freq=100000)
 print(i2c.scan())   # 例: 0x3e=文字, 0x62=RGB
 # 表示には JHD1313/AIP31068 ドライバを使用</t>
-  </si>
-  <si>
-    <t>101020010</t>
   </si>
   <si>
     <t>display</t>
@@ -597,9 +510,6 @@
     print(dist_cm()); time.sleep(0.3)</t>
   </si>
   <si>
-    <t>101020046</t>
-  </si>
-  <si>
     <t>Grove - Hall Sensor</t>
   </si>
   <si>
@@ -609,9 +519,6 @@
     <t>回転数/速度計測、磁石位置検出、近接スイッチ。</t>
   </si>
   <si>
-    <t>101020049</t>
-  </si>
-  <si>
     <t>Grove - Flame Sensor</t>
   </si>
   <si>
@@ -621,9 +528,6 @@
     <t>火災・炎検知、防火アラーム、燃焼監視。</t>
   </si>
   <si>
-    <t>101020037</t>
-  </si>
-  <si>
     <t>Grove - Touch Sensor</t>
   </si>
   <si>
@@ -631,9 +535,6 @@
   </si>
   <si>
     <t>タッチスイッチ、非接触ボタン、静電操作パネル。</t>
-  </si>
-  <si>
-    <t>101020039</t>
   </si>
   <si>
     <t>Grove - 3-Axis Digital Accelerometer(±1.5g)</t>
@@ -657,9 +558,6 @@
     time.sleep(0.2)</t>
   </si>
   <si>
-    <t>105020003</t>
-  </si>
-  <si>
     <t>Grove - Vibration Motor</t>
   </si>
   <si>
@@ -674,9 +572,6 @@
 motor = Pin(9, Pin.OUT)
 motor.value(1); time.sleep(0.3)   # 振動
 motor.value(0)</t>
-  </si>
-  <si>
-    <t>104030003</t>
   </si>
   <si>
     <t>Grove - 4-Digit Display</t>
@@ -699,9 +594,6 @@
 tm.number(1234)</t>
   </si>
   <si>
-    <t>107020001</t>
-  </si>
-  <si>
     <t>Grove - Speaker</t>
   </si>
   <si>
@@ -719,9 +611,6 @@
 spk.duty_u16(0)</t>
   </si>
   <si>
-    <t>101020013</t>
-  </si>
-  <si>
     <t>Grove - RTC</t>
   </si>
   <si>
@@ -739,9 +628,6 @@
 print(bcd(d[2]), bcd(d[1]), bcd(d[0]))  # 時 分 秒</t>
   </si>
   <si>
-    <t>104020006</t>
-  </si>
-  <si>
     <t>Grove LED Bar v2.0</t>
   </si>
   <si>
@@ -760,9 +646,6 @@
 clk = Pin(9, Pin.OUT)   # 黄=DCKI
 dat = Pin(8, Pin.OUT)   # 白=DI
 # bar = GroveLedBar(clk, dat); bar.level(5)</t>
-  </si>
-  <si>
-    <t>104020131</t>
   </si>
   <si>
     <t>Grove - RGB LED Stick (10 - WS2813 Mini)</t>
@@ -912,6 +795,162 @@
   </si>
   <si>
     <t>Product Name</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>111020063</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020732</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020733</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020734</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020735</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020736</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>104020188</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>107020089</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>111020066</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020737</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>111020064</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020738</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020739</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>111020065</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>104020189</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>104020190</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>111020067</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>104020195</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>104020196</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>111020068</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>109020001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>111020069</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>111020070</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>111020071</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020740</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020741</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020742</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>109020002</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020743</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020744</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020745</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020746</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>101020747</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>108020121</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>104020192</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>107020090</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>109020003</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>104020193</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>104020194</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1370,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>2</v>
@@ -1379,16 +1418,16 @@
         <v>3</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>215</v>
+        <v>176</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>4</v>
@@ -1399,1272 +1438,1272 @@
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="11" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="36" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="36" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="36" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>196</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="36" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>197</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="36" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="36" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="36" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="36" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>62</v>
+        <v>201</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="36" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="36" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>71</v>
+        <v>203</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="36" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="36" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="36" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>94</v>
+        <v>207</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="36" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>98</v>
+        <v>208</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="36" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="36" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J21" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="36" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="36" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>123</v>
+        <v>213</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="36" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>131</v>
+        <v>215</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F26" s="11"/>
       <c r="G26" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="36" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>135</v>
+        <v>216</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="36" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="36" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>144</v>
+        <v>218</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="14.25" customHeight="1">
       <c r="A30" s="3">
-        <v>104020111</v>
+        <v>104020191</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="36" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J32" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="K32" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="36" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="36" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>169</v>
+        <v>222</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J34" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K34" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="K34" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="36" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
       <c r="H35" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="36" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="36" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="E37" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F37" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>225</v>
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="18" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>191</v>
-      </c>
       <c r="E38" s="11" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="36" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
       <c r="H39" s="11" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="36" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>201</v>
+        <v>163</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>226</v>
+        <v>187</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="36" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="11" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>210</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/GroveCreaterKit.xlsx
+++ b/GroveCreaterKit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/watanabekoichi/Developments/Claude_Projects/I0630_M5StackMicroPythonToolkit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD5B9CC-E0D2-234F-9418-235DFA7B1DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935B3404-2099-8F40-A8A0-191EDADAA01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="840" windowWidth="30240" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="231">
   <si>
     <t>SKU</t>
   </si>
@@ -381,15 +381,6 @@
     <t>PORT.B（ボタン=G9 / LED=G8）</t>
   </si>
   <si>
-    <t>from machine import Pin
-import time
-btn = Pin(9, Pin.IN)    # 黄=ボタン
-led = Pin(8, Pin.OUT)   # 白=LED
-while True:
-    led.value(btn.value())
-    time.sleep(0.05)</t>
-  </si>
-  <si>
     <t>Grove - Yellow LED Button</t>
   </si>
   <si>
@@ -474,12 +465,6 @@
   </si>
   <si>
     <t>PORT.A（I2C: SCL=G1 / SDA=G2）</t>
-  </si>
-  <si>
-    <t>from machine import Pin, I2C
-i2c = I2C(0, scl=Pin(1), sda=Pin(2), freq=100000)
-print(i2c.scan())   # 例: 0x3e=文字, 0x62=RGB
-# 表示には JHD1313/AIP31068 ドライバを使用</t>
   </si>
   <si>
     <t>display</t>
@@ -953,12 +938,148 @@
     <t>104020194</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">from machine import Pin
+import time
+btn = Pin(9, Pin.IN)    # </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>黄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="2"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ボタン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+led = Pin(8, Pin.OUT)   # </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>白</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="2"/>
+      </rPr>
+      <t>=LED
+while True:
+    led.value(btn.value())
+    time.sleep(0.05)</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">from machine import Pin, I2C
+i2c = I2C(0, scl=Pin(1), sda=Pin(2), freq=100000)
+print(i2c.scan())   # </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 0x3e=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>文字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, 0x62=RGB
+# </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>表示には</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> JHD1313/AIP31068 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ドライバを使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>※別途、専用ドライバを入れる必要あり。</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,6 +1122,12 @@
       <sz val="9"/>
       <name val="Consolas"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="MS Mincho"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1409,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>2</v>
@@ -1418,16 +1545,16 @@
         <v>3</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>4</v>
@@ -1438,7 +1565,7 @@
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -1453,12 +1580,14 @@
         <v>9</v>
       </c>
       <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
+      <c r="G2" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="H2" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>10</v>
@@ -1469,7 +1598,7 @@
     </row>
     <row r="3" spans="1:11" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
@@ -1484,12 +1613,14 @@
         <v>15</v>
       </c>
       <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="H3" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>16</v>
@@ -1500,7 +1631,7 @@
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>18</v>
@@ -1516,13 +1647,13 @@
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>10</v>
@@ -1533,7 +1664,7 @@
     </row>
     <row r="5" spans="1:11" ht="36" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>18</v>
@@ -1548,12 +1679,14 @@
         <v>25</v>
       </c>
       <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="G5" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="H5" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>16</v>
@@ -1564,7 +1697,7 @@
     </row>
     <row r="6" spans="1:11" ht="36" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -1579,12 +1712,14 @@
         <v>29</v>
       </c>
       <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="G6" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="H6" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>16</v>
@@ -1595,7 +1730,7 @@
     </row>
     <row r="7" spans="1:11" ht="36" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>18</v>
@@ -1611,13 +1746,13 @@
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H7" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>16</v>
@@ -1628,7 +1763,7 @@
     </row>
     <row r="8" spans="1:11" ht="36" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>18</v>
@@ -1645,10 +1780,10 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>36</v>
@@ -1659,7 +1794,7 @@
     </row>
     <row r="9" spans="1:11" ht="36" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -1676,10 +1811,10 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>42</v>
@@ -1690,7 +1825,7 @@
     </row>
     <row r="10" spans="1:11" ht="36" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>44</v>
@@ -1705,14 +1840,12 @@
         <v>47</v>
       </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="11" t="s">
-        <v>189</v>
-      </c>
+      <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>10</v>
@@ -1723,7 +1856,7 @@
     </row>
     <row r="11" spans="1:11" ht="36" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>48</v>
@@ -1740,10 +1873,10 @@
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>10</v>
@@ -1754,7 +1887,7 @@
     </row>
     <row r="12" spans="1:11" ht="36" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>18</v>
@@ -1771,10 +1904,10 @@
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>36</v>
@@ -1785,7 +1918,7 @@
     </row>
     <row r="13" spans="1:11" ht="36" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>44</v>
@@ -1802,10 +1935,10 @@
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>10</v>
@@ -1816,7 +1949,7 @@
     </row>
     <row r="14" spans="1:11" ht="36" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>18</v>
@@ -1832,13 +1965,13 @@
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>62</v>
@@ -1849,7 +1982,7 @@
     </row>
     <row r="15" spans="1:11" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -1866,10 +1999,10 @@
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>67</v>
@@ -1880,7 +2013,7 @@
     </row>
     <row r="16" spans="1:11" ht="36" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1895,14 +2028,14 @@
         <v>71</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>72</v>
@@ -1913,7 +2046,7 @@
     </row>
     <row r="17" spans="1:11" ht="36" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>38</v>
@@ -1930,10 +2063,10 @@
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>36</v>
@@ -1944,7 +2077,7 @@
     </row>
     <row r="18" spans="1:11" ht="36" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>38</v>
@@ -1959,12 +2092,14 @@
         <v>80</v>
       </c>
       <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="G18" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="H18" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>10</v>
@@ -1975,7 +2110,7 @@
     </row>
     <row r="19" spans="1:11" ht="36" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>48</v>
@@ -1991,13 +2126,13 @@
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>36</v>
@@ -2008,7 +2143,7 @@
     </row>
     <row r="20" spans="1:11" ht="36" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>38</v>
@@ -2024,13 +2159,13 @@
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>36</v>
@@ -2041,7 +2176,7 @@
     </row>
     <row r="21" spans="1:11" ht="36" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>38</v>
@@ -2056,12 +2191,14 @@
         <v>89</v>
       </c>
       <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="G21" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="H21" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>10</v>
@@ -2072,7 +2209,7 @@
     </row>
     <row r="22" spans="1:11" ht="36" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>48</v>
@@ -2087,14 +2224,14 @@
         <v>92</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>93</v>
@@ -2105,7 +2242,7 @@
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>95</v>
@@ -2122,61 +2259,61 @@
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>99</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>100</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="36" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>102</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>103</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>99</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>106</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>98</v>
@@ -2184,43 +2321,43 @@
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>99</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="36" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="E26" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>109</v>
       </c>
       <c r="F26" s="11"/>
       <c r="G26" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H26" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I26" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>16</v>
@@ -2231,62 +2368,60 @@
     </row>
     <row r="27" spans="1:11" ht="36" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="E27" s="11" t="s">
         <v>111</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>112</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>10</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="36" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>116</v>
-      </c>
       <c r="F28" s="11"/>
-      <c r="G28" s="11" t="s">
-        <v>189</v>
-      </c>
+      <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I28" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>16</v>
@@ -2297,33 +2432,33 @@
     </row>
     <row r="29" spans="1:11" ht="36" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>10</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="14.25" customHeight="1">
@@ -2334,85 +2469,87 @@
         <v>95</v>
       </c>
       <c r="C30" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="F30" s="11"/>
+      <c r="F30" s="11" t="s">
+        <v>230</v>
+      </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>125</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="36" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="E31" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>129</v>
       </c>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>10</v>
@@ -2423,27 +2560,27 @@
     </row>
     <row r="33" spans="1:11" ht="36" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>135</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>137</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I33" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>16</v>
@@ -2454,27 +2591,27 @@
     </row>
     <row r="34" spans="1:11" ht="36" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>140</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>10</v>
@@ -2485,225 +2622,227 @@
     </row>
     <row r="35" spans="1:11" ht="36" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>143</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
       <c r="H35" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="36" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
+      <c r="G36" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="H36" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>36</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="36" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C37" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>151</v>
-      </c>
       <c r="F37" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="18" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>154</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>156</v>
       </c>
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>42</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="36" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>160</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
       <c r="H39" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="36" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>164</v>
-      </c>
       <c r="F40" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="36" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E41" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D41" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>169</v>
-      </c>
       <c r="F41" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/GroveCreaterKit.xlsx
+++ b/GroveCreaterKit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/watanabekoichi/Developments/Claude_Projects/I0630_M5StackMicroPythonToolkit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935B3404-2099-8F40-A8A0-191EDADAA01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACD8C7E-0FB4-0946-9FB5-72F9789D69CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="840" windowWidth="30240" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="231">
   <si>
     <t>SKU</t>
   </si>
@@ -1679,9 +1679,7 @@
         <v>25</v>
       </c>
       <c r="F5" s="11"/>
-      <c r="G5" s="11" t="s">
-        <v>187</v>
-      </c>
+      <c r="G5" s="11"/>
       <c r="H5" s="11" t="s">
         <v>170</v>
       </c>

--- a/GroveCreaterKit.xlsx
+++ b/GroveCreaterKit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/watanabekoichi/Developments/Claude_Projects/I0630_M5StackMicroPythonToolkit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACD8C7E-0FB4-0946-9FB5-72F9789D69CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C9DF57-2FAC-354A-B3EE-A8BBAD281221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="840" windowWidth="30240" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="235">
   <si>
     <t>SKU</t>
   </si>
@@ -1074,12 +1074,46 @@
     <t>※別途、専用ドライバを入れる必要あり。</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>専用ドライバのアップロード必要</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">センヨウ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ノアップロードヘ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t xml:space="preserve">ヒツヨウ </t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ビコウ </t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>UIFlow2 v2.4.7 に標準 dht モジュールが無く、Python のビットバングでは 1-Wire のμsタイミングが不安定で応答を取得できない（no response）。CoreS3 では安定動作しないため Level1 から除外。温度のみなら Temperature Sensor（サーミスタ）で代替可。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>M5Stack CoreS3は3.7V環境のためリニアな入力が難しいためLevel1より除外</t>
+    <rPh sb="19" eb="21">
+      <t xml:space="preserve">カンキョウ </t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t xml:space="preserve">ニュウリョク </t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1129,8 +1163,15 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1151,6 +1192,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1198,7 +1245,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1231,6 +1278,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1513,7 +1569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="19.1640625" customWidth="1"/>
@@ -1526,9 +1582,10 @@
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="60" customWidth="1"/>
+    <col min="12" max="12" width="57.83203125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18" customHeight="1">
+    <row r="1" spans="1:12" ht="18" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1562,8 +1619,11 @@
       <c r="K1" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="36" customHeight="1">
+      <c r="L1" s="13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="36" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>189</v>
       </c>
@@ -1595,8 +1655,9 @@
       <c r="K2" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="36" customHeight="1">
+      <c r="L2" s="14"/>
+    </row>
+    <row r="3" spans="1:12" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>190</v>
       </c>
@@ -1628,8 +1689,9 @@
       <c r="K3" s="12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="36" customHeight="1">
+      <c r="L3" s="14"/>
+    </row>
+    <row r="4" spans="1:12" ht="36" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>191</v>
       </c>
@@ -1661,8 +1723,9 @@
       <c r="K4" s="12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="36" customHeight="1">
+      <c r="L4" s="14"/>
+    </row>
+    <row r="5" spans="1:12" ht="36" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>192</v>
       </c>
@@ -1692,8 +1755,11 @@
       <c r="K5" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="36" customHeight="1">
+      <c r="L5" s="14" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="36" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>193</v>
       </c>
@@ -1725,8 +1791,9 @@
       <c r="K6" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="36" customHeight="1">
+      <c r="L6" s="14"/>
+    </row>
+    <row r="7" spans="1:12" ht="36" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>194</v>
       </c>
@@ -1758,8 +1825,9 @@
       <c r="K7" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="36" customHeight="1">
+      <c r="L7" s="14"/>
+    </row>
+    <row r="8" spans="1:12" ht="36" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>195</v>
       </c>
@@ -1789,8 +1857,9 @@
       <c r="K8" s="12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="36" customHeight="1">
+      <c r="L8" s="14"/>
+    </row>
+    <row r="9" spans="1:12" ht="36" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>196</v>
       </c>
@@ -1820,8 +1889,9 @@
       <c r="K9" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="36" customHeight="1">
+      <c r="L9" s="14"/>
+    </row>
+    <row r="10" spans="1:12" ht="36" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>197</v>
       </c>
@@ -1851,8 +1921,9 @@
       <c r="K10" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="36" customHeight="1">
+      <c r="L10" s="14"/>
+    </row>
+    <row r="11" spans="1:12" ht="36" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>198</v>
       </c>
@@ -1882,8 +1953,9 @@
       <c r="K11" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="36" customHeight="1">
+      <c r="L11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" ht="36" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>199</v>
       </c>
@@ -1913,8 +1985,9 @@
       <c r="K12" s="12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="36" customHeight="1">
+      <c r="L12" s="14"/>
+    </row>
+    <row r="13" spans="1:12" ht="36" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>200</v>
       </c>
@@ -1944,8 +2017,9 @@
       <c r="K13" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="36" customHeight="1">
+      <c r="L13" s="14"/>
+    </row>
+    <row r="14" spans="1:12" ht="36" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>201</v>
       </c>
@@ -1961,7 +2035,9 @@
       <c r="E14" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="11" t="s">
+        <v>231</v>
+      </c>
       <c r="G14" s="11" t="s">
         <v>187</v>
       </c>
@@ -1977,8 +2053,11 @@
       <c r="K14" s="12" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="36" customHeight="1">
+      <c r="L14" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>202</v>
       </c>
@@ -2008,8 +2087,9 @@
       <c r="K15" s="12" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="36" customHeight="1">
+      <c r="L15" s="14"/>
+    </row>
+    <row r="16" spans="1:12" ht="36" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>203</v>
       </c>
@@ -2041,8 +2121,9 @@
       <c r="K16" s="12" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="36" customHeight="1">
+      <c r="L16" s="14"/>
+    </row>
+    <row r="17" spans="1:12" ht="36" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>204</v>
       </c>
@@ -2072,8 +2153,9 @@
       <c r="K17" s="12" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="36" customHeight="1">
+      <c r="L17" s="14"/>
+    </row>
+    <row r="18" spans="1:12" ht="36" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>205</v>
       </c>
@@ -2105,8 +2187,9 @@
       <c r="K18" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="36" customHeight="1">
+      <c r="L18" s="14"/>
+    </row>
+    <row r="19" spans="1:12" ht="36" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>206</v>
       </c>
@@ -2138,8 +2221,9 @@
       <c r="K19" s="12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="36" customHeight="1">
+      <c r="L19" s="14"/>
+    </row>
+    <row r="20" spans="1:12" ht="36" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>207</v>
       </c>
@@ -2171,8 +2255,9 @@
       <c r="K20" s="12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="36" customHeight="1">
+      <c r="L20" s="14"/>
+    </row>
+    <row r="21" spans="1:12" ht="36" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>208</v>
       </c>
@@ -2204,8 +2289,9 @@
       <c r="K21" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="36" customHeight="1">
+      <c r="L21" s="14"/>
+    </row>
+    <row r="22" spans="1:12" ht="36" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>209</v>
       </c>
@@ -2237,8 +2323,9 @@
       <c r="K22" s="12" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="36" customHeight="1">
+      <c r="L22" s="14"/>
+    </row>
+    <row r="23" spans="1:12" ht="36" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>210</v>
       </c>
@@ -2268,8 +2355,9 @@
       <c r="K23" s="12" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="36" customHeight="1">
+      <c r="L23" s="14"/>
+    </row>
+    <row r="24" spans="1:12" ht="36" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>211</v>
       </c>
@@ -2299,8 +2387,9 @@
       <c r="K24" s="12" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="36" customHeight="1">
+      <c r="L24" s="14"/>
+    </row>
+    <row r="25" spans="1:12" ht="36" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>212</v>
       </c>
@@ -2330,8 +2419,9 @@
       <c r="K25" s="12" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="36" customHeight="1">
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" spans="1:12" ht="36" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>213</v>
       </c>
@@ -2363,8 +2453,9 @@
       <c r="K26" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="36" customHeight="1">
+      <c r="L26" s="14"/>
+    </row>
+    <row r="27" spans="1:12" ht="36" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>214</v>
       </c>
@@ -2396,8 +2487,9 @@
       <c r="K27" s="12" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="36" customHeight="1">
+      <c r="L27" s="14"/>
+    </row>
+    <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>215</v>
       </c>
@@ -2427,8 +2519,9 @@
       <c r="K28" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="36" customHeight="1">
+      <c r="L28" s="14"/>
+    </row>
+    <row r="29" spans="1:12" ht="36" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>216</v>
       </c>
@@ -2458,8 +2551,9 @@
       <c r="K29" s="12" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1">
+      <c r="L29" s="14"/>
+    </row>
+    <row r="30" spans="1:12" ht="14.25" customHeight="1">
       <c r="A30" s="3">
         <v>104020191</v>
       </c>
@@ -2491,8 +2585,9 @@
       <c r="K30" s="12" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="36" customHeight="1">
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="1:12" ht="36" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>217</v>
       </c>
@@ -2524,8 +2619,9 @@
       <c r="K31" s="12" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="18" customHeight="1">
+      <c r="L31" s="14"/>
+    </row>
+    <row r="32" spans="1:12" ht="18" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>218</v>
       </c>
@@ -2555,8 +2651,9 @@
       <c r="K32" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="36" customHeight="1">
+      <c r="L32" s="14"/>
+    </row>
+    <row r="33" spans="1:12" ht="36" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>219</v>
       </c>
@@ -2586,8 +2683,9 @@
       <c r="K33" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="36" customHeight="1">
+      <c r="L33" s="14"/>
+    </row>
+    <row r="34" spans="1:12" ht="36" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>220</v>
       </c>
@@ -2617,8 +2715,9 @@
       <c r="K34" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="36" customHeight="1">
+      <c r="L34" s="14"/>
+    </row>
+    <row r="35" spans="1:12" ht="36" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>221</v>
       </c>
@@ -2648,8 +2747,9 @@
       <c r="K35" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="36" customHeight="1">
+      <c r="L35" s="14"/>
+    </row>
+    <row r="36" spans="1:12" ht="36" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>222</v>
       </c>
@@ -2681,8 +2781,9 @@
       <c r="K36" s="12" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" ht="36" customHeight="1">
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" spans="1:12" ht="36" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>223</v>
       </c>
@@ -2714,8 +2815,9 @@
       <c r="K37" s="12" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="18" customHeight="1">
+      <c r="L37" s="14"/>
+    </row>
+    <row r="38" spans="1:12" ht="18" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>224</v>
       </c>
@@ -2745,8 +2847,9 @@
       <c r="K38" s="12" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" ht="36" customHeight="1">
+      <c r="L38" s="14"/>
+    </row>
+    <row r="39" spans="1:12" ht="36" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>225</v>
       </c>
@@ -2776,8 +2879,9 @@
       <c r="K39" s="12" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" ht="36" customHeight="1">
+      <c r="L39" s="14"/>
+    </row>
+    <row r="40" spans="1:12" ht="36" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>226</v>
       </c>
@@ -2809,8 +2913,9 @@
       <c r="K40" s="12" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" ht="36" customHeight="1">
+      <c r="L40" s="14"/>
+    </row>
+    <row r="41" spans="1:12" ht="36" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>227</v>
       </c>
@@ -2842,6 +2947,7 @@
       <c r="K41" s="12" t="s">
         <v>169</v>
       </c>
+      <c r="L41" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>

--- a/GroveCreaterKit.xlsx
+++ b/GroveCreaterKit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/watanabekoichi/Developments/Claude_Projects/I0630_M5StackMicroPythonToolkit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C9DF57-2FAC-354A-B3EE-A8BBAD281221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D94AA0-C52C-2E47-B938-6DCF6F842A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="840" windowWidth="30240" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3560" windowWidth="30240" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="237">
   <si>
     <t>SKU</t>
   </si>
@@ -1105,6 +1105,20 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t xml:space="preserve">ニュウリョク </t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>5V動作のアナログ温度センサ。CoreS3(3.3V)ではSIGがADC上限に張り付く／逆に大半でGND付近にフローティングし、正しい室温は瞬間的にしか読めない。ケーブル交換・挿し直しでも改善せず安定動作しないためLevel1から除外。温度が必要な場合はI2C接続の温湿度センサ（例: ENVユニット）で代替を推奨。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>動作不良のため、level1対象外とした。</t>
+    <rPh sb="2" eb="4">
+      <t xml:space="preserve">フリョウノタメ </t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t xml:space="preserve">タイショウガイ </t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -1657,7 +1671,7 @@
       </c>
       <c r="L2" s="14"/>
     </row>
-    <row r="3" spans="1:12" ht="36" customHeight="1">
+    <row r="3" spans="1:12" ht="97" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>190</v>
       </c>
@@ -1674,9 +1688,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
-        <v>187</v>
-      </c>
+      <c r="G3" s="11"/>
       <c r="H3" s="11" t="s">
         <v>175</v>
       </c>
@@ -1689,7 +1701,9 @@
       <c r="K3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="14" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="4" spans="1:12" ht="36" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -2019,7 +2033,7 @@
       </c>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="1:12" ht="36" customHeight="1">
+    <row r="14" spans="1:12" ht="72" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>201</v>
       </c>
@@ -2472,9 +2486,7 @@
         <v>111</v>
       </c>
       <c r="F27" s="11"/>
-      <c r="G27" s="11" t="s">
-        <v>187</v>
-      </c>
+      <c r="G27" s="11"/>
       <c r="H27" s="11" t="s">
         <v>170</v>
       </c>
@@ -2487,7 +2499,9 @@
       <c r="K27" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="L27" s="14"/>
+      <c r="L27" s="14" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="1" t="s">

--- a/GroveCreaterKit.xlsx
+++ b/GroveCreaterKit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/watanabekoichi/Developments/Claude_Projects/I0630_M5StackMicroPythonToolkit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D94AA0-C52C-2E47-B938-6DCF6F842A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67994C60-AFEF-DE48-856C-497BFF3483BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3560" windowWidth="30240" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2100" windowWidth="30240" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="236">
   <si>
     <t>SKU</t>
   </si>
@@ -76,17 +76,6 @@
   </si>
   <si>
     <t>PORT.B（アナログ/ADC: 黄=G9）</t>
-  </si>
-  <si>
-    <t>from machine import Pin, ADC
-import math, time
-adc = ADC(Pin(9)); adc.atten(ADC.ATTN_11DB)
-B = 4275; R0 = 100000   # NCP18WF104 (v1.2)
-while True:
-    v = adc.read_u16()
-    r = R0 * (65535.0 / v - 1.0)
-    t = 1/(math.log(r/R0)/B + 1/298.15) - 273.15
-    print('%.1f C' % t); time.sleep(1)</t>
   </si>
   <si>
     <t>sensor</t>
@@ -1109,10 +1098,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>5V動作のアナログ温度センサ。CoreS3(3.3V)ではSIGがADC上限に張り付く／逆に大半でGND付近にフローティングし、正しい室温は瞬間的にしか読めない。ケーブル交換・挿し直しでも改善せず安定動作しないためLevel1から除外。温度が必要な場合はI2C接続の温湿度センサ（例: ENVユニット）で代替を推奨。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>動作不良のため、level1対象外とした。</t>
     <rPh sb="2" eb="4">
       <t xml:space="preserve">フリョウノタメ </t>
@@ -1120,6 +1105,18 @@
     <rPh sb="14" eb="17">
       <t xml:space="preserve">タイショウガイ </t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>from machine import Pin, ADC
+import math, time
+adc = ADC(Pin(9)); adc.atten(ADC.ATTN_11DB)
+B = 4275; R0 = 100000   # NCP18WF104 (v1.2)
+while True:
+    v = adc.read_u16()
+    r = R0 * (65535.0 / v - 1.0)
+    t = 1/(math.log(r/R0)/B + 1/298.15) - 273.15
+    print('%.1f C' % t); time.sleep(1)</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1607,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>2</v>
@@ -1616,16 +1613,16 @@
         <v>3</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H1" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>4</v>
@@ -1634,12 +1631,12 @@
         <v>5</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -1655,13 +1652,13 @@
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H2" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>10</v>
@@ -1673,7 +1670,7 @@
     </row>
     <row r="3" spans="1:12" ht="97" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
@@ -1688,246 +1685,246 @@
         <v>15</v>
       </c>
       <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>186</v>
+      </c>
       <c r="H3" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>16</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="14" t="s">
         <v>235</v>
       </c>
+      <c r="L3" s="14"/>
     </row>
     <row r="4" spans="1:12" ht="36" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>21</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H4" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L4" s="14"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="36" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>29</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="1:12" ht="36" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>35</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>37</v>
       </c>
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="1:12" ht="36" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="12" t="s">
         <v>42</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="1:12" ht="36" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>10</v>
@@ -1939,27 +1936,27 @@
     </row>
     <row r="11" spans="1:12" ht="36" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>51</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>10</v>
@@ -1971,59 +1968,59 @@
     </row>
     <row r="12" spans="1:12" ht="36" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>54</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="1:12" ht="36" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>58</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>10</v>
@@ -2035,165 +2032,161 @@
     </row>
     <row r="14" spans="1:12" ht="72" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="E14" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="F14" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="J14" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="J14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="12" t="s">
-        <v>63</v>
-      </c>
       <c r="L14" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>66</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J15" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="K15" s="12" t="s">
         <v>67</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>68</v>
       </c>
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="1:12" ht="36" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="F16" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J16" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" s="12" t="s">
         <v>72</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>73</v>
       </c>
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="1:12" ht="36" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" ht="36" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="E18" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>80</v>
-      </c>
       <c r="F18" s="11"/>
-      <c r="G18" s="11" t="s">
-        <v>187</v>
-      </c>
+      <c r="G18" s="11"/>
       <c r="H18" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I18" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>10</v>
@@ -2205,97 +2198,95 @@
     </row>
     <row r="19" spans="1:12" ht="36" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="E19" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>83</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>37</v>
       </c>
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12" ht="36" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>85</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>86</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J20" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>37</v>
       </c>
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="1:12" ht="36" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>89</v>
-      </c>
       <c r="F21" s="11"/>
-      <c r="G21" s="11" t="s">
-        <v>187</v>
-      </c>
+      <c r="G21" s="11"/>
       <c r="H21" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>10</v>
@@ -2307,263 +2298,263 @@
     </row>
     <row r="22" spans="1:12" ht="36" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="F22" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J22" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>94</v>
       </c>
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="1:12" ht="36" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="1:12" ht="36" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L24" s="14"/>
     </row>
     <row r="25" spans="1:12" ht="36" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>105</v>
-      </c>
       <c r="E25" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="1:12" ht="36" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="E26" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>108</v>
       </c>
       <c r="F26" s="11"/>
       <c r="G26" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="1:12" ht="36" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="E27" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I27" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>10</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="1:12" ht="36" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>117</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>10</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L29" s="14"/>
     </row>
@@ -2572,92 +2563,92 @@
         <v>104020191</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>122</v>
-      </c>
       <c r="F30" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="1:12" ht="36" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H31" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I31" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="I31" s="11" t="s">
-        <v>171</v>
-      </c>
       <c r="J31" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="K31" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>129</v>
       </c>
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="1:12" ht="18" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="E32" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>132</v>
       </c>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I32" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>10</v>
@@ -2669,59 +2660,61 @@
     </row>
     <row r="33" spans="1:12" ht="36" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="E33" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>16</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="1:12" ht="36" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="E34" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="11" t="s">
-        <v>138</v>
-      </c>
       <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
+      <c r="G34" s="11" t="s">
+        <v>186</v>
+      </c>
       <c r="H34" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I34" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>10</v>
@@ -2733,233 +2726,233 @@
     </row>
     <row r="35" spans="1:12" ht="36" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="E35" s="11" t="s">
         <v>140</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>141</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
       <c r="H35" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L35" s="14"/>
     </row>
     <row r="36" spans="1:12" ht="36" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="E36" s="11" t="s">
         <v>144</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>145</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="1:12" ht="36" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="E37" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="E37" s="11" t="s">
-        <v>149</v>
-      </c>
       <c r="F37" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J37" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="K37" s="12" t="s">
         <v>150</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>151</v>
       </c>
       <c r="L37" s="14"/>
     </row>
     <row r="38" spans="1:12" ht="18" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="E38" s="11" t="s">
         <v>153</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>154</v>
       </c>
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L38" s="14"/>
     </row>
     <row r="39" spans="1:12" ht="36" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="E39" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>158</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
       <c r="H39" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="1:12" ht="36" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="E40" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="E40" s="11" t="s">
-        <v>162</v>
-      </c>
       <c r="F40" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J40" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="K40" s="12" t="s">
         <v>163</v>
-      </c>
-      <c r="K40" s="12" t="s">
-        <v>164</v>
       </c>
       <c r="L40" s="14"/>
     </row>
     <row r="41" spans="1:12" ht="36" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="E41" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="E41" s="11" t="s">
-        <v>167</v>
-      </c>
       <c r="F41" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J41" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="K41" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="K41" s="12" t="s">
-        <v>169</v>
       </c>
       <c r="L41" s="14"/>
     </row>
